--- a/data/2026/counties_2026.xlsx
+++ b/data/2026/counties_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\naughtm\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846AA4A3-E8AB-40B6-B9B8-86E80E44583B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E288C029-AD56-49AF-9AFA-2792372942E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="795" windowWidth="21600" windowHeight="11295" xr2:uid="{72E2CD52-C6E9-4078-9EF8-51B607413A01}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{72E2CD52-C6E9-4078-9EF8-51B607413A01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,13 +116,13 @@
     <t>Wicklow</t>
   </si>
   <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
     <t>Issued</t>
   </si>
   <si>
     <t>Refused</t>
+  </si>
+  <si>
+    <t>County</t>
   </si>
 </sst>
 </file>
@@ -193,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -202,7 +202,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,315 +536,306 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C53B2E0F-97AC-4AA7-9EA7-8614B7E1812A}">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="B1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="4">
-        <v>12219</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1499</v>
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>78</v>
+      </c>
+      <c r="C2" s="2">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="C3" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>156</v>
+        <v>268</v>
       </c>
       <c r="C4" s="2">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>268</v>
+        <v>1241</v>
       </c>
       <c r="C5" s="2">
-        <v>28</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1241</v>
+        <v>145</v>
       </c>
       <c r="C6" s="2">
-        <v>171</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>145</v>
+        <v>5515</v>
       </c>
       <c r="C7" s="2">
-        <v>17</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>5515</v>
+        <v>421</v>
       </c>
       <c r="C8" s="2">
-        <v>661</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>421</v>
+        <v>354</v>
       </c>
       <c r="C9" s="2">
-        <v>76</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>354</v>
+        <v>532</v>
       </c>
       <c r="C10" s="2">
-        <v>19</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>532</v>
+        <v>154</v>
       </c>
       <c r="C11" s="2">
-        <v>93</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="C12" s="2">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="C13" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>50</v>
+        <v>527</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>527</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2">
-        <v>93</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>54</v>
+        <v>244</v>
       </c>
       <c r="C16" s="2">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>244</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>136</v>
+        <v>648</v>
       </c>
       <c r="C18" s="2">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>648</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="C20" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="C21" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="C22" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>238</v>
+        <v>364</v>
       </c>
       <c r="C24" s="2">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>364</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>154</v>
+        <v>296</v>
       </c>
       <c r="C26" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>296</v>
+        <v>143</v>
       </c>
       <c r="C27" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2">
-        <v>143</v>
-      </c>
-      <c r="C28" s="2">
         <v>25</v>
       </c>
     </row>
@@ -855,6 +845,45 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </m02c691f3efa402dab5cbaa8c240a9e7>
+    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Value>5</Value>
+      <Value>1</Value>
+    </TaxCatchAll>
+    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
+    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
+        </TermInfo>
+      </Terms>
+    </h1f8bb4843d6459a8b809123185593c7>
+    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </fbaa881fc4ae443f9fdafbdd527793df>
+    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
+    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </nb1b8a72855341e18dd75ce464e281f2>
+    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
+    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
+        </TermInfo>
+      </Terms>
+    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="eDocument" ma:contentTypeID="0x0101000BC94875665D404BB1351B53C41FD2C000E5CBA74D75A77049B177D97877D56E03" ma:contentTypeVersion="199" ma:contentTypeDescription="" ma:contentTypeScope="" ma:versionID="f29b0ff1a26a7575c948acee1be83c00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f94102a1-1d6c-4502-ac27-91905b9321dd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3fe347a261331acec84421138fd81903" ns2:_="">
     <xsd:import namespace="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
@@ -1063,45 +1092,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <m02c691f3efa402dab5cbaa8c240a9e7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </m02c691f3efa402dab5cbaa8c240a9e7>
-    <TaxCatchAll xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Value>5</Value>
-      <Value>1</Value>
-    </TaxCatchAll>
-    <eDocs_FileStatus xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">Live</eDocs_FileStatus>
-    <h1f8bb4843d6459a8b809123185593c7 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">218</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">d1f665d0-1ea2-48c4-9fae-9dfb881d0110</TermId>
-        </TermInfo>
-      </Terms>
-    </h1f8bb4843d6459a8b809123185593c7>
-    <fbaa881fc4ae443f9fdafbdd527793df xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </fbaa881fc4ae443f9fdafbdd527793df>
-    <_vti_ItemDeclaredRecord xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <nb1b8a72855341e18dd75ce464e281f2 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </nb1b8a72855341e18dd75ce464e281f2>
-    <eDocs_eFileName xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd" xsi:nil="true"/>
-    <mbbd3fafa5ab4e5eb8a6a5e099cef439 xmlns="f94102a1-1d6c-4502-ac27-91905b9321dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">Unclassified</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">779752a3-a421-4077-839c-91815f544ae2</TermId>
-        </TermInfo>
-      </Terms>
-    </mbbd3fafa5ab4e5eb8a6a5e099cef439>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1112,6 +1102,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13E55B9-09DE-41F3-803E-8153BD24572F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC3BD01-9F0E-4BB6-AE14-B67BE94AD123}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1129,22 +1135,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D13E55B9-09DE-41F3-803E-8153BD24572F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f94102a1-1d6c-4502-ac27-91905b9321dd"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{962A8ADF-5395-4BCA-8071-DEA864AD0C16}">
   <ds:schemaRefs>
